--- a/csp-guru/csp-guru.xlsx
+++ b/csp-guru/csp-guru.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9dc17ffb94daae5c/Documents/GitHub/csp-guru/csp-guru/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\azolan\Documents\GitHub\csp-guru\csp-guru\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="643" documentId="13_ncr:1_{093ED339-6936-4CC1-B3D4-C8350AA4EC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0420DE7C-04F1-49BE-A36C-F06F545851EF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EB254A-8843-41C2-9D0D-333CEFEE65EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{CBAE575A-07C4-4BF8-8763-A77EB57639B5}"/>
+    <workbookView xWindow="3105" yWindow="2910" windowWidth="14400" windowHeight="8175" xr2:uid="{CBAE575A-07C4-4BF8-8763-A77EB57639B5}"/>
   </bookViews>
   <sheets>
     <sheet name="csp-guru" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7433" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7442" uniqueCount="1344">
   <si>
     <t>Power_station</t>
   </si>
@@ -4072,6 +4072,15 @@
   </si>
   <si>
     <t>Waad Al-Shama ISCC</t>
+  </si>
+  <si>
+    <t>100MW Tower CSP+8 HRS TES</t>
+  </si>
+  <si>
+    <t>1 GW PV</t>
+  </si>
+  <si>
+    <t>TsingTao</t>
   </si>
 </sst>
 </file>
@@ -4190,14 +4199,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4235,7 +4240,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4341,7 +4346,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4483,7 +4488,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4492,104 +4497,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{932C9696-B96D-4ED0-ACF8-5A8E00AFA897}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:CP155"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:CP156"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55" customWidth="1"/>
-    <col min="2" max="2" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="35.1796875" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="35.140625" customWidth="1"/>
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.7265625" customWidth="1"/>
-    <col min="14" max="14" width="23.7265625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="47.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="42.1796875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="42.1796875" customWidth="1"/>
-    <col min="25" max="25" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="42.140625" customWidth="1"/>
+    <col min="25" max="25" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="34.42578125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="19" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="43.453125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="46.26953125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="60.7265625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="45.453125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="57.1796875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="57.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="38" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="31.1796875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="48" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="39.1796875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="81.1796875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="68.54296875" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="35.453125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="74.54296875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="53.1796875" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="61.1796875" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="36.54296875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="37.81640625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="42.81640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="68.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="74.5703125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="72" max="72" width="40" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="60.7265625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="72.453125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="23.1796875" style="5" customWidth="1"/>
-    <col min="81" max="81" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="72.42578125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="23.140625" style="5" customWidth="1"/>
+    <col min="81" max="81" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="35" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="23.7265625" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="38.26953125" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="34.453125" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="25.26953125" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="81.1796875" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="81.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4873,7 +4878,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -5078,7 +5083,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>112</v>
       </c>
@@ -5280,7 +5285,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>118</v>
       </c>
@@ -5482,7 +5487,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="5" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>124</v>
       </c>
@@ -5684,7 +5689,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="6" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>125</v>
       </c>
@@ -5886,7 +5891,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="7" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>127</v>
       </c>
@@ -6088,7 +6093,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="8" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>128</v>
       </c>
@@ -6290,7 +6295,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="9" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -6492,7 +6497,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="10" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -6694,7 +6699,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>134</v>
       </c>
@@ -6905,7 +6910,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>146</v>
       </c>
@@ -7146,7 +7151,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>166</v>
       </c>
@@ -7372,7 +7377,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>188</v>
       </c>
@@ -7625,7 +7630,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>208</v>
       </c>
@@ -7814,7 +7819,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>219</v>
       </c>
@@ -8067,7 +8072,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>222</v>
       </c>
@@ -8253,7 +8258,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>232</v>
       </c>
@@ -8494,7 +8499,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>245</v>
       </c>
@@ -8729,7 +8734,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>254</v>
       </c>
@@ -8955,7 +8960,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>258</v>
       </c>
@@ -9162,7 +9167,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>275</v>
       </c>
@@ -9397,7 +9402,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>281</v>
       </c>
@@ -9632,7 +9637,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>282</v>
       </c>
@@ -9867,7 +9872,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>283</v>
       </c>
@@ -10087,7 +10092,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>295</v>
       </c>
@@ -10340,7 +10345,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>305</v>
       </c>
@@ -10593,7 +10598,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>307</v>
       </c>
@@ -10846,7 +10851,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>315</v>
       </c>
@@ -11084,7 +11089,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>320</v>
       </c>
@@ -11260,7 +11265,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>331</v>
       </c>
@@ -11474,7 +11479,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>339</v>
       </c>
@@ -11712,7 +11717,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>344</v>
       </c>
@@ -11892,7 +11897,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>353</v>
       </c>
@@ -12133,7 +12138,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>362</v>
       </c>
@@ -12377,7 +12382,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>371</v>
       </c>
@@ -12606,7 +12611,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>383</v>
       </c>
@@ -12847,7 +12852,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>390</v>
       </c>
@@ -13065,7 +13070,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>400</v>
       </c>
@@ -13273,7 +13278,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>408</v>
       </c>
@@ -13476,7 +13481,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>415</v>
       </c>
@@ -13729,7 +13734,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>418</v>
       </c>
@@ -13906,7 +13911,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>429</v>
       </c>
@@ -14141,7 +14146,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>439</v>
       </c>
@@ -14394,7 +14399,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>446</v>
       </c>
@@ -14647,7 +14652,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>448</v>
       </c>
@@ -14885,7 +14890,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>449</v>
       </c>
@@ -15129,7 +15134,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>453</v>
       </c>
@@ -15379,7 +15384,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>459</v>
       </c>
@@ -15626,7 +15631,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>463</v>
       </c>
@@ -15873,7 +15878,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>468</v>
       </c>
@@ -16071,7 +16076,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>476</v>
       </c>
@@ -16322,7 +16327,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>485</v>
       </c>
@@ -16518,7 +16523,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>503</v>
       </c>
@@ -16771,7 +16776,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>504</v>
       </c>
@@ -16936,7 +16941,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>510</v>
       </c>
@@ -17177,7 +17182,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="57" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>514</v>
       </c>
@@ -17418,7 +17423,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>515</v>
       </c>
@@ -17662,7 +17667,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>523</v>
       </c>
@@ -17906,7 +17911,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>525</v>
       </c>
@@ -18144,7 +18149,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>531</v>
       </c>
@@ -18337,7 +18342,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>538</v>
       </c>
@@ -18569,7 +18574,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>545</v>
       </c>
@@ -18764,7 +18769,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>551</v>
       </c>
@@ -19008,7 +19013,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>553</v>
       </c>
@@ -19228,7 +19233,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>556</v>
       </c>
@@ -19463,7 +19468,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>561</v>
       </c>
@@ -19704,7 +19709,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>565</v>
       </c>
@@ -19945,7 +19950,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>566</v>
       </c>
@@ -20186,7 +20191,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>570</v>
       </c>
@@ -20427,7 +20432,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>571</v>
       </c>
@@ -20644,7 +20649,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>585</v>
       </c>
@@ -20882,7 +20887,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>594</v>
       </c>
@@ -21081,7 +21086,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>601</v>
       </c>
@@ -21325,7 +21330,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>605</v>
       </c>
@@ -21560,7 +21565,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>611</v>
       </c>
@@ -21795,7 +21800,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>619</v>
       </c>
@@ -21977,7 +21982,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>629</v>
       </c>
@@ -22206,7 +22211,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="79" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>639</v>
       </c>
@@ -22447,7 +22452,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="80" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>641</v>
       </c>
@@ -22688,7 +22693,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>642</v>
       </c>
@@ -22929,7 +22934,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>649</v>
       </c>
@@ -23164,7 +23169,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="83" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>668</v>
       </c>
@@ -23396,7 +23401,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="84" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>674</v>
       </c>
@@ -23628,7 +23633,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="85" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>676</v>
       </c>
@@ -23842,7 +23847,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>686</v>
       </c>
@@ -24057,7 +24062,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>693</v>
       </c>
@@ -24261,7 +24266,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>703</v>
       </c>
@@ -24490,7 +24495,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>713</v>
       </c>
@@ -24719,7 +24724,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>724</v>
       </c>
@@ -24957,7 +24962,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>735</v>
       </c>
@@ -25177,7 +25182,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="92" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>739</v>
       </c>
@@ -25361,7 +25366,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>746</v>
       </c>
@@ -25587,7 +25592,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="94" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>761</v>
       </c>
@@ -25810,7 +25815,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>770</v>
       </c>
@@ -26034,7 +26039,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="96" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>783</v>
       </c>
@@ -26220,7 +26225,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="97" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>788</v>
       </c>
@@ -26427,7 +26432,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="98" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>796</v>
       </c>
@@ -26660,7 +26665,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="99" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>804</v>
       </c>
@@ -26837,7 +26842,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="100" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>815</v>
       </c>
@@ -27057,7 +27062,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>823</v>
       </c>
@@ -27270,7 +27275,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="102" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>831</v>
       </c>
@@ -27454,7 +27459,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>838</v>
       </c>
@@ -27654,7 +27659,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="104" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>847</v>
       </c>
@@ -27859,7 +27864,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>855</v>
       </c>
@@ -28112,7 +28117,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="106" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>868</v>
       </c>
@@ -28321,7 +28326,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="107" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>880</v>
       </c>
@@ -28547,7 +28552,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="108" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>888</v>
       </c>
@@ -28722,7 +28727,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>894</v>
       </c>
@@ -28946,7 +28951,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="110" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>902</v>
       </c>
@@ -29167,7 +29172,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>904</v>
       </c>
@@ -29408,7 +29413,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="112" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>912</v>
       </c>
@@ -29649,7 +29654,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="113" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>917</v>
       </c>
@@ -29860,7 +29865,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="114" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>921</v>
       </c>
@@ -30073,7 +30078,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="115" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>934</v>
       </c>
@@ -30293,7 +30298,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="116" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>941</v>
       </c>
@@ -30534,7 +30539,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="117" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>957</v>
       </c>
@@ -30763,7 +30768,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="118" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>963</v>
       </c>
@@ -30971,7 +30976,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="119" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1233</v>
       </c>
@@ -31145,7 +31150,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="120" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>981</v>
       </c>
@@ -31358,7 +31363,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="121" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>988</v>
       </c>
@@ -31579,7 +31584,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="122" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1000</v>
       </c>
@@ -31808,7 +31813,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="123" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1012</v>
       </c>
@@ -32004,7 +32009,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="124" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1268</v>
       </c>
@@ -32206,7 +32211,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="125" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1038</v>
       </c>
@@ -32429,7 +32434,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="126" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1053</v>
       </c>
@@ -32670,7 +32675,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="127" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1074</v>
       </c>
@@ -32849,7 +32854,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="128" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>1087</v>
       </c>
@@ -33022,7 +33027,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="129" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1296</v>
       </c>
@@ -33211,7 +33216,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="130" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1094</v>
       </c>
@@ -33405,7 +33410,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="131" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1103</v>
       </c>
@@ -33585,7 +33590,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="132" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1110</v>
       </c>
@@ -33752,7 +33757,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="133" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1119</v>
       </c>
@@ -33935,7 +33940,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="134" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1124</v>
       </c>
@@ -34102,7 +34107,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="135" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1125</v>
       </c>
@@ -34251,7 +34256,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="136" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1128</v>
       </c>
@@ -34431,7 +34436,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="137" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1130</v>
       </c>
@@ -34601,7 +34606,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="138" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>1132</v>
       </c>
@@ -34765,7 +34770,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="139" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1136</v>
       </c>
@@ -34951,7 +34956,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="140" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1267</v>
       </c>
@@ -35122,7 +35127,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="141" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1141</v>
       </c>
@@ -35254,7 +35259,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="142" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1269</v>
       </c>
@@ -35379,7 +35384,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="143" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1299</v>
       </c>
@@ -35544,7 +35549,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="144" spans="1:94" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:94" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1292</v>
       </c>
@@ -35685,7 +35690,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="145" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1293</v>
       </c>
@@ -35780,7 +35785,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="146" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1270</v>
       </c>
@@ -35925,7 +35930,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="147" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>1271</v>
       </c>
@@ -36062,7 +36067,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="148" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>1272</v>
       </c>
@@ -36188,7 +36193,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="149" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1284</v>
       </c>
@@ -36325,7 +36330,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="150" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1288</v>
       </c>
@@ -36453,7 +36458,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="151" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>1285</v>
       </c>
@@ -36542,7 +36547,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="152" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>1246</v>
       </c>
@@ -36613,7 +36618,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="153" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>1273</v>
       </c>
@@ -36706,7 +36711,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="154" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1316</v>
       </c>
@@ -36882,7 +36887,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="155" spans="1:94" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
         <v>1315</v>
       </c>
@@ -37069,6 +37074,50 @@
       <c r="CO155" s="8"/>
       <c r="CP155" s="8" t="s">
         <v>1339</v>
+      </c>
+    </row>
+    <row r="156" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C156">
+        <v>159</v>
+      </c>
+      <c r="D156" t="s">
+        <v>487</v>
+      </c>
+      <c r="E156" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F156" t="s">
+        <v>119</v>
+      </c>
+      <c r="G156">
+        <v>100</v>
+      </c>
+      <c r="K156" t="s">
+        <v>167</v>
+      </c>
+      <c r="P156">
+        <v>2025</v>
+      </c>
+      <c r="Q156">
+        <v>2025</v>
+      </c>
+      <c r="R156" t="s">
+        <v>487</v>
+      </c>
+      <c r="S156" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BH156">
+        <v>8</v>
+      </c>
+      <c r="BI156" t="s">
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -37093,14 +37142,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A22E0AF-49D6-4719-823A-410668FCC514}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1224</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1218</v>
       </c>
@@ -37108,13 +37157,13 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1300</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1213</v>
       </c>
@@ -37125,7 +37174,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1215</v>
       </c>
@@ -37133,7 +37182,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1217</v>
       </c>
@@ -37141,7 +37190,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1220</v>
       </c>
@@ -37149,7 +37198,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1222</v>
       </c>
@@ -37178,4 +37227,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>